--- a/assets/BOs/Thor.xlsx
+++ b/assets/BOs/Thor.xlsx
@@ -5,20 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\OneDrive\Github\DoD\DeitiesOfDeath\public\assets\BOs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\doc\coding\DoD\DeitiesOfDeath\public\assets\BOs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E15D917-EF36-452E-93AD-A6D0F61B0C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B92F065-8CD2-4207-89A6-DB8A2A610ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5535" yWindow="5670" windowWidth="43200" windowHeight="23445" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil4" sheetId="5" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
-    <sheet name="Feuil1" sheetId="2" r:id="rId3"/>
-    <sheet name="Feuil3" sheetId="4" r:id="rId4"/>
-    <sheet name="Feuil2" sheetId="3" r:id="rId5"/>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId6"/>
+    <sheet name="Feuil5" sheetId="7" r:id="rId1"/>
+    <sheet name="Feuil4" sheetId="5" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId3"/>
+    <sheet name="Feuil1" sheetId="2" r:id="rId4"/>
+    <sheet name="Feuil3" sheetId="4" r:id="rId5"/>
+    <sheet name="Feuil2" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="176">
   <si>
     <t>Archaic</t>
   </si>
@@ -107,30 +107,6 @@
     <t>1 dwarf to gold</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">0 / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / 4 / 0</t>
-    </r>
-  </si>
-  <si>
     <t>Research Copper Armor, this dwarf will go to wood</t>
   </si>
   <si>
@@ -158,20 +134,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / 2 / 5 / 0</t>
-    </r>
-  </si>
-  <si>
     <t>1 dwarf to food</t>
   </si>
   <si>
@@ -181,39 +143,6 @@
     <t>Berserker builds a house after Copper Shields</t>
   </si>
   <si>
-    <r>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / 5 / 0</t>
-    </r>
-  </si>
-  <si>
     <t>7 dwarves to food</t>
   </si>
   <si>
@@ -226,66 +155,10 @@
     <t>Advance (3.36)</t>
   </si>
   <si>
-    <r>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / 3 / 5 / 0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / 4 / 0</t>
-    </r>
-  </si>
-  <si>
     <t>Move 4 dwarves from food and gold to wood</t>
   </si>
   <si>
     <t>Classical (4.36)</t>
-  </si>
-  <si>
-    <t>Dwarven Armory V2 - Mirez</t>
-  </si>
-  <si>
-    <t>2 gatherer to wood</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=iyERSRwVEkw</t>
   </si>
   <si>
     <t>Auto Queue Dwarves/ Stop Vill Auto Queue (Let first vill train tho)</t>
@@ -1744,13 +1617,267 @@
   </si>
   <si>
     <t>https://youtu.be/Wv-A-dG0YMA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">0 / 0 / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">0 / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 3 / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>1 gather to wood</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">0 / 1 / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">0 / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 4 / 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">0 / 2 / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 2 / 5 / 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 5 / 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 3 / 5 / 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> / 4 / 0</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Build an ox cart for wood </t>
+  </si>
+  <si>
+    <t>Dwarven Armory V3 - By Mirez</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1990,6 +2117,12 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -2092,7 +2225,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2103,7 +2236,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -2178,6 +2310,9 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2189,6 +2324,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2204,39 +2366,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Lien hypertexte 2" xfId="3" xr:uid="{B11739F6-FDE6-4BD0-8C36-0CFEE279B9F8}"/>
     <cellStyle name="Lien hypertexte 3" xfId="5" xr:uid="{D29B8A2A-638D-4148-93BE-FD685B793A86}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2518,25 +2662,262 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0E4BF3E-266F-457B-B6E3-6E696CBB80AF}">
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18">
+      <c r="A1" s="59" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.6">
+      <c r="A2" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="67" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="67"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="67" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="67" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="67" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="67"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="67" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="67" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="67" t="s">
+        <v>171</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="67" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.6">
+      <c r="A11" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="67"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="67" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="67" t="s">
+        <v>173</v>
+      </c>
+      <c r="B14" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" s="66"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.6">
+      <c r="A15" s="61" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="67" t="s">
+        <v>173</v>
+      </c>
+      <c r="B17" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="66"/>
+      <c r="D17" s="68"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="63"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.6">
+      <c r="A21" s="69"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="66"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.6">
+      <c r="A22" s="69"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.6">
+      <c r="A23" s="69"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="71"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="66"/>
+      <c r="D24" s="66"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.6">
+      <c r="A25" s="70"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="71"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.6">
+      <c r="A27" s="70"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="66"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A20:D20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{004DB6AC-EA08-4AC5-8440-1378E785A924}">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" customWidth="1"/>
-    <col min="2" max="2" width="50.42578125" customWidth="1"/>
-    <col min="3" max="3" width="62.5703125" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" customWidth="1"/>
+    <col min="2" max="2" width="50.44140625" customWidth="1"/>
+    <col min="3" max="3" width="62.5546875" customWidth="1"/>
     <col min="4" max="4" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75">
+    <row r="1" spans="1:4" ht="18">
       <c r="A1" s="45" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
       <c r="D1" s="46"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" ht="15.6">
       <c r="A2" s="47" t="s">
         <v>0</v>
       </c>
@@ -2544,176 +2925,176 @@
       <c r="C2" s="46"/>
       <c r="D2" s="46"/>
     </row>
-    <row r="3" spans="1:4" ht="15">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:4" ht="14.4">
+      <c r="A3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-    </row>
-    <row r="4" spans="1:4" ht="30">
-      <c r="A4" s="33" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+    </row>
+    <row r="4" spans="1:4" ht="28.8">
+      <c r="A4" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="31"/>
+    </row>
+    <row r="5" spans="1:4" ht="14.4">
+      <c r="A5" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="31"/>
+    </row>
+    <row r="6" spans="1:4" ht="14.4">
+      <c r="A6" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+    </row>
+    <row r="7" spans="1:4" ht="14.4">
+      <c r="A7" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B7" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C7" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="D4" s="32"/>
-    </row>
-    <row r="5" spans="1:4" ht="15">
-      <c r="A5" s="33" t="s">
+      <c r="D7" s="31"/>
+    </row>
+    <row r="8" spans="1:4" ht="14.4">
+      <c r="A8" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B8" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+    </row>
+    <row r="9" spans="1:4" ht="14.4">
+      <c r="A9" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="32"/>
-    </row>
-    <row r="6" spans="1:4" ht="15">
-      <c r="A6" s="33" t="s">
+      <c r="B9" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="D9" s="31"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.6">
+      <c r="A10" s="48" t="s">
         <v>128</v>
-      </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-    </row>
-    <row r="7" spans="1:4" ht="15">
-      <c r="A7" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7" s="32"/>
-    </row>
-    <row r="8" spans="1:4" ht="15">
-      <c r="A8" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-    </row>
-    <row r="9" spans="1:4" ht="15">
-      <c r="A9" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" s="32"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="48" t="s">
-        <v>136</v>
       </c>
       <c r="B10" s="46"/>
       <c r="C10" s="46"/>
       <c r="D10" s="46"/>
     </row>
-    <row r="11" spans="1:4" s="32" customFormat="1" ht="15">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:4" s="31" customFormat="1" ht="14.4">
+      <c r="A11" s="31" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15">
-      <c r="A12" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="D12" s="32"/>
-    </row>
-    <row r="13" spans="1:4" ht="15">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-    </row>
-    <row r="14" spans="1:4" ht="15">
-      <c r="A14" s="36"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-    </row>
-    <row r="15" spans="1:4">
+    <row r="12" spans="1:4" ht="14.4">
+      <c r="A12" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="31"/>
+    </row>
+    <row r="13" spans="1:4" ht="14.4">
+      <c r="A13" s="31"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+    </row>
+    <row r="14" spans="1:4" ht="14.4">
+      <c r="A14" s="35"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.6">
       <c r="A15" s="48" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B15" s="46"/>
       <c r="C15" s="46"/>
       <c r="D15" s="46"/>
     </row>
-    <row r="16" spans="1:4" ht="15">
-      <c r="A16" s="32" t="s">
+    <row r="16" spans="1:4" ht="14.4">
+      <c r="A16" s="31" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15">
-      <c r="A17" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="B17" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="D17" s="39"/>
-    </row>
-    <row r="18" spans="1:4" ht="15">
-      <c r="C18" s="40"/>
-    </row>
-    <row r="19" spans="1:4" ht="15">
-      <c r="A19" s="41" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15">
+    <row r="17" spans="1:4" ht="14.4">
+      <c r="A17" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" s="38"/>
+    </row>
+    <row r="18" spans="1:4" ht="14.4">
+      <c r="C18" s="39"/>
+    </row>
+    <row r="19" spans="1:4" ht="14.4">
+      <c r="A19" s="40" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="14.4">
       <c r="A20" s="49"/>
       <c r="B20" s="46"/>
       <c r="C20" s="46"/>
       <c r="D20" s="46"/>
     </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="42"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="42"/>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="42"/>
-      <c r="B23" s="43"/>
-    </row>
-    <row r="24" spans="1:4" ht="15">
-      <c r="A24" s="44"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="43"/>
-    </row>
-    <row r="26" spans="1:4" ht="15">
-      <c r="A26" s="44"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="43"/>
+    <row r="21" spans="1:4" ht="15.6">
+      <c r="A21" s="41"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.6">
+      <c r="A22" s="41"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.6">
+      <c r="A23" s="41"/>
+      <c r="B23" s="42"/>
+    </row>
+    <row r="24" spans="1:4" ht="14.4">
+      <c r="A24" s="43"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.6">
+      <c r="A25" s="42"/>
+    </row>
+    <row r="26" spans="1:4" ht="14.4">
+      <c r="A26" s="43"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.6">
+      <c r="A27" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2727,28 +3108,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE1FD85-23DD-4C9B-A5CB-EA2608B12DC1}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" thickBot="1">
-      <c r="A1" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="62"/>
-    </row>
-    <row r="2" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A2" s="57" t="s">
+    <row r="1" spans="1:4" ht="18" thickBot="1">
+      <c r="A1" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="52"/>
+    </row>
+    <row r="2" spans="1:4" ht="16.2" thickBot="1">
+      <c r="A2" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="59"/>
-    </row>
-    <row r="3" spans="1:4" ht="58.5" thickBot="1">
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="55"/>
+    </row>
+    <row r="3" spans="1:4" ht="56.4" thickBot="1">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2756,7 +3137,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" ht="58.5" thickBot="1">
+    <row r="4" spans="1:4" ht="56.4" thickBot="1">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2768,7 +3149,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" ht="30.75" thickBot="1">
+    <row r="5" spans="1:4" ht="28.8" thickBot="1">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -2778,31 +3159,31 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" ht="115.5" thickBot="1">
+    <row r="6" spans="1:4" ht="111.6" thickBot="1">
       <c r="A6" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" ht="30" thickBot="1">
+    <row r="7" spans="1:4" ht="28.8" thickBot="1">
       <c r="A7" s="1" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:4" ht="30.75" thickBot="1">
+    <row r="8" spans="1:4" ht="28.8" thickBot="1">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>10</v>
@@ -2810,55 +3191,55 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" ht="115.5" thickBot="1">
+    <row r="9" spans="1:4" ht="111.6" thickBot="1">
       <c r="A9" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" ht="84" thickBot="1">
+      <c r="A10" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="111.6" thickBot="1">
+      <c r="A11" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="1" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="16.2" thickBot="1">
+      <c r="A12" s="53" t="s">
         <v>152</v>
       </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" ht="87" thickBot="1">
-      <c r="A10" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="115.5" thickBot="1">
-      <c r="A11" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A12" s="57" t="s">
-        <v>160</v>
-      </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="59"/>
-    </row>
-    <row r="13" spans="1:4" ht="58.5" thickBot="1">
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="55"/>
+    </row>
+    <row r="13" spans="1:4" ht="56.4" thickBot="1">
       <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
@@ -2866,9 +3247,9 @@
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:4" ht="44.25" thickBot="1">
+    <row r="14" spans="1:4" ht="42.6" thickBot="1">
       <c r="A14" s="1" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="1" t="s">
@@ -2878,27 +3259,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="115.5" thickBot="1">
+    <row r="15" spans="1:4" ht="111.6" thickBot="1">
       <c r="A15" s="3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A16" s="57" t="s">
-        <v>164</v>
-      </c>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="59"/>
-    </row>
-    <row r="17" spans="1:4" ht="58.5" thickBot="1">
+    <row r="16" spans="1:4" ht="16.2" thickBot="1">
+      <c r="A16" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="55"/>
+    </row>
+    <row r="17" spans="1:4" ht="56.4" thickBot="1">
       <c r="A17" s="1" t="s">
         <v>1</v>
       </c>
@@ -2906,48 +3287,48 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" ht="39.75" thickBot="1">
+    <row r="18" spans="1:4" ht="40.799999999999997" thickBot="1">
       <c r="A18" s="3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" ht="90.75" thickBot="1">
+    <row r="19" spans="1:4" ht="93.6" thickBot="1">
       <c r="A19" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" ht="15.75" thickBot="1">
+    <row r="20" spans="1:4" ht="15" thickBot="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A21" s="64"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="65"/>
-      <c r="D21" s="66"/>
-    </row>
-    <row r="22" spans="1:4" ht="60.75" thickBot="1">
-      <c r="A22" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="B22" s="63" t="s">
-        <v>171</v>
+    <row r="21" spans="1:4" ht="15" thickBot="1">
+      <c r="A21" s="56"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="58"/>
+    </row>
+    <row r="22" spans="1:4" ht="58.2" thickBot="1">
+      <c r="A22" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="B22" s="44" t="s">
+        <v>163</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -2967,301 +3348,301 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6680AA3C-660E-4512-8311-360274DD2AC9}">
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75">
-      <c r="A1" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="52" t="s">
+    <row r="1" spans="1:4" ht="18">
+      <c r="A1" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.6">
+      <c r="A2" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="14"/>
-      <c r="B4" s="15" t="s">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="14" t="s">
+      <c r="B7" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="6"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="14" t="s">
+      <c r="B8" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="C8" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="B9" s="14" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="14" t="s">
+      <c r="C9" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="D9" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="15" t="s">
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="14" t="s">
+      <c r="B10" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="C10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="14" t="s">
+      <c r="B11" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="C11" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="14" t="s">
+      <c r="C12" s="14"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B13" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.6">
+      <c r="A15" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="14" t="s">
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="D16" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="15" t="s">
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="14" t="s">
+      <c r="D17" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="15" t="s">
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="14" t="s">
+      <c r="B18" s="5"/>
+      <c r="C18" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="15" t="s">
+      <c r="D18" s="14"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75">
-      <c r="A15" s="53" t="s">
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.6">
+      <c r="A21" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="16" t="s">
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="4"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D23" s="16" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="16" t="s">
+    <row r="24" spans="1:4">
+      <c r="A24" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="B24" s="4"/>
+      <c r="C24" s="16" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="14" t="s">
+      <c r="D24" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="15" t="s">
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="12"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="15"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="15"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="7"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75">
-      <c r="A21" s="53" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" s="51"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="5"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="13"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" s="16"/>
+      <c r="D25" s="15"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="54"/>
-      <c r="B26" s="51"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-    </row>
-    <row r="27" spans="1:4" ht="15.75">
-      <c r="A27" s="10"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="5"/>
-    </row>
-    <row r="28" spans="1:4" ht="15.75">
-      <c r="A28" s="10"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-    </row>
-    <row r="29" spans="1:4" ht="15.75">
-      <c r="A29" s="10"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="A26" s="63"/>
+      <c r="B26" s="60"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.6">
+      <c r="A27" s="9"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.6">
+      <c r="A28" s="9"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.6">
+      <c r="A29" s="9"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="12"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-    </row>
-    <row r="31" spans="1:4" ht="15.75">
-      <c r="A31" s="11"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.6">
+      <c r="A31" s="10"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="12"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-    </row>
-    <row r="33" spans="1:1" ht="15.75">
-      <c r="A33" s="11"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+    </row>
+    <row r="33" spans="1:1" ht="15.6">
+      <c r="A33" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3275,132 +3656,132 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8CCFC68-0746-4C6F-BCC1-F86EACB19062}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" thickBot="1">
-      <c r="A1" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-    </row>
-    <row r="2" spans="1:3" ht="16.5" thickBot="1">
-      <c r="A2" s="28" t="s">
+    <row r="1" spans="1:3" ht="18" thickBot="1">
+      <c r="A1" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+    </row>
+    <row r="2" spans="1:3" ht="16.2" thickBot="1">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-    </row>
-    <row r="3" spans="1:3" ht="48" thickBot="1">
-      <c r="A3" s="31" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+    </row>
+    <row r="3" spans="1:3" ht="47.4" thickBot="1">
+      <c r="A3" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="211.2" thickBot="1">
+      <c r="A4" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="166.2" thickBot="1">
+      <c r="A5" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="25"/>
+    </row>
+    <row r="6" spans="1:3" ht="151.19999999999999" thickBot="1">
+      <c r="A6" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B6" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C6" s="25" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="226.5" thickBot="1">
-      <c r="A4" s="26" t="s">
+    <row r="7" spans="1:3" ht="76.2" thickBot="1">
+      <c r="A7" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="166.5" thickBot="1">
-      <c r="A5" s="26" t="s">
+    <row r="8" spans="1:3" ht="61.2" thickBot="1">
+      <c r="A8" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="26"/>
-    </row>
-    <row r="6" spans="1:3" ht="151.5" thickBot="1">
-      <c r="A6" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="26" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="331.2" thickBot="1">
+      <c r="A9" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="B9" s="29" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="76.5" thickBot="1">
-      <c r="A7" s="26" t="s">
+      <c r="C9" s="29"/>
+    </row>
+    <row r="10" spans="1:3" ht="31.8" thickBot="1">
+      <c r="A10" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+    </row>
+    <row r="11" spans="1:3" ht="121.2" thickBot="1">
+      <c r="A11" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="B11" s="25" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="61.5" thickBot="1">
-      <c r="A8" s="26" t="s">
+      <c r="C11" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="26" t="s">
+    </row>
+    <row r="12" spans="1:3" ht="16.2" thickBot="1">
+      <c r="A12" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+    </row>
+    <row r="13" spans="1:3" ht="346.2" thickBot="1">
+      <c r="A13" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="B13" s="24" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="361.5" thickBot="1">
-      <c r="A9" s="26" t="s">
+      <c r="C13" s="25" t="s">
         <v>110</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" s="30"/>
-    </row>
-    <row r="10" spans="1:3" ht="32.25" thickBot="1">
-      <c r="A10" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-    </row>
-    <row r="11" spans="1:3" ht="136.5" thickBot="1">
-      <c r="A11" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="16.5" thickBot="1">
-      <c r="A12" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-    </row>
-    <row r="13" spans="1:3" ht="361.5" thickBot="1">
-      <c r="A13" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -3408,174 +3789,174 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8687E243-15B1-41C8-AC08-9FC8810D84BA}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75">
-      <c r="A1" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="53" t="s">
+    <row r="1" spans="1:4" ht="18">
+      <c r="A1" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.6">
+      <c r="A2" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-    </row>
-    <row r="4" spans="1:4" ht="75">
-      <c r="A4" s="14" t="s">
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+    </row>
+    <row r="4" spans="1:4" ht="72">
+      <c r="A4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="14"/>
+    </row>
+    <row r="6" spans="1:4" ht="86.4">
+      <c r="A6" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="21" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="15.6">
+      <c r="A7" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+    </row>
+    <row r="9" spans="1:4" ht="158.4">
+      <c r="A9" s="14" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="14" t="s">
+      <c r="B9" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="C9" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D9" s="19"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.6">
+      <c r="A10" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="15"/>
-    </row>
-    <row r="6" spans="1:4" ht="90">
-      <c r="A6" s="14" t="s">
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+    </row>
+    <row r="11" spans="1:4" ht="86.4">
+      <c r="A11" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="22" t="s">
+      <c r="C11" s="22" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75">
-      <c r="A7" s="53" t="s">
+      <c r="D11" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-    </row>
-    <row r="9" spans="1:4" ht="165">
-      <c r="A9" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="20"/>
-    </row>
-    <row r="10" spans="1:4" ht="15.75">
-      <c r="A10" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-    </row>
-    <row r="11" spans="1:4" ht="105">
-      <c r="A11" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="15"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="18"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="17"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="5"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="13"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="56"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-    </row>
-    <row r="16" spans="1:4" ht="15.75">
-      <c r="A16" s="10"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:2" ht="15.75">
-      <c r="A17" s="10"/>
-      <c r="B17" s="5"/>
-    </row>
-    <row r="18" spans="1:2" ht="15.75">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
+      <c r="A15" s="65"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+    </row>
+    <row r="16" spans="1:4" ht="15.6">
+      <c r="A16" s="9"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:2" ht="15.6">
+      <c r="A17" s="9"/>
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" spans="1:2" ht="15.6">
+      <c r="A18" s="9"/>
+      <c r="B18" s="10"/>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="5"/>
-    </row>
-    <row r="20" spans="1:2" ht="15.75">
-      <c r="A20" s="11"/>
-      <c r="B20" s="5"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" spans="1:2" ht="15.6">
+      <c r="A20" s="10"/>
+      <c r="B20" s="4"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="12"/>
-      <c r="B21" s="5"/>
-    </row>
-    <row r="22" spans="1:2" ht="15.75">
-      <c r="A22" s="11"/>
-      <c r="B22" s="5"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="4"/>
+    </row>
+    <row r="22" spans="1:2" ht="15.6">
+      <c r="A22" s="10"/>
+      <c r="B22" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3587,196 +3968,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="57.140625" customWidth="1"/>
-    <col min="3" max="3" width="52.28515625" customWidth="1"/>
-    <col min="4" max="4" width="56.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="36" customHeight="1" thickBot="1">
-      <c r="A1" s="60" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="62"/>
-    </row>
-    <row r="2" spans="1:4" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A2" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="59"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A10" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="59"/>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A14" s="57" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="59"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:D10"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A17" r:id="rId1" tooltip="https://www.youtube.com/watch?v=iyERSRwVEkw" xr:uid="{0DA9C09D-46DA-49C3-B619-6B30D7DB887E}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>